--- a/templates/10_mame_gc_prenormalised.xlsx
+++ b/templates/10_mame_gc_prenormalised.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WT</t>
+          <t>A1</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -441,70 +441,210 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Q232A</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.85</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y233A</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A40P</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E61Y</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L150V</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A40P_E61Y</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.11</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>blank</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>0.01</v>
       </c>
     </row>
